--- a/Data/appliance_efficiencies.xlsx
+++ b/Data/appliance_efficiencies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud-my.sharepoint.com/personal/dominic_jones_grattaninstitute_edu_au/Documents/Energy/Analysis/analysis_cp_dj_2025/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="8_{2735264D-2E0F-4466-B96E-5FAF4E87C276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC91E12F-FAEA-4F5F-9A6B-952DC6D126F4}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="8_{2735264D-2E0F-4466-B96E-5FAF4E87C276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4680F1E1-2576-4C60-A557-74B529A208AB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{5D07E076-C928-4160-91FA-0417357B04A5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5D07E076-C928-4160-91FA-0417357B04A5}"/>
   </bookViews>
   <sheets>
     <sheet name="coefficients" sheetId="5" r:id="rId1"/>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="1" hidden="1">'hot water'!$A$1:$C$7</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -153,9 +153,6 @@
     <t>Water heating</t>
   </si>
   <si>
-    <t>Space conditioning</t>
-  </si>
-  <si>
     <t>https://cao-94612.s3.amazonaws.com/documents/Induction-Range-Final-Report-July-2019.pdf</t>
   </si>
   <si>
@@ -217,6 +214,9 @@
   </si>
   <si>
     <t>Represents RCAC heating and cooling relative to ducted gas</t>
+  </si>
+  <si>
+    <t>Space conditioning - heating</t>
   </si>
 </sst>
 </file>
@@ -269,7 +269,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -277,7 +277,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -405,6 +404,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -772,13 +775,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84206C80-EF8B-460E-AD2F-5661B8B796F3}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>28</v>
       </c>
@@ -786,7 +789,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -795,10 +798,10 @@
         <v>0.42805755395683454</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -807,19 +810,19 @@
         <v>0.80584122538955694</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B4">
         <f>'space heating'!C4</f>
         <v>0.24109589041095891</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -830,9 +833,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29FE9849-F102-4ED9-ACB3-E3D3A1532CE6}">
   <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -846,13 +849,13 @@
         <v>17</v>
       </c>
       <c r="E1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -872,7 +875,7 @@
 kWh/year]]+Table003__Page_3[[#This Row],[gas usage kwh]]</f>
         <v>3407</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2">
         <f>3407/Table003__Page_3[[#This Row],[total_energy_kwh]]</f>
         <v>1</v>
       </c>
@@ -880,7 +883,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -900,7 +903,7 @@
 kWh/year]]+Table003__Page_3[[#This Row],[gas usage kwh]]</f>
         <v>4496.6500000000005</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3">
         <f>3407/Table003__Page_3[[#This Row],[total_energy_kwh]]</f>
         <v>0.75767515817330666</v>
       </c>
@@ -908,7 +911,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -928,12 +931,12 @@
 kWh/year]]+Table003__Page_3[[#This Row],[gas usage kwh]]</f>
         <v>4227.88</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4">
         <f>3407/Table003__Page_3[[#This Row],[total_energy_kwh]]</f>
         <v>0.80584122538955694</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -953,12 +956,12 @@
 kWh/year]]+Table003__Page_3[[#This Row],[gas usage kwh]]</f>
         <v>510</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5">
         <f>3407/Table003__Page_3[[#This Row],[total_energy_kwh]]</f>
         <v>6.6803921568627453</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -978,12 +981,12 @@
 kWh/year]]+Table003__Page_3[[#This Row],[gas usage kwh]]</f>
         <v>757</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6">
         <f>3407/Table003__Page_3[[#This Row],[total_energy_kwh]]</f>
         <v>4.500660501981506</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1003,7 +1006,7 @@
 kWh/year]]+Table003__Page_3[[#This Row],[gas usage kwh]]</f>
         <v>1771</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7">
         <f>3407/Table003__Page_3[[#This Row],[total_energy_kwh]]</f>
         <v>1.9237718802936195</v>
       </c>
@@ -1020,9 +1023,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B1B825-ADD3-43AD-A4F4-B092E031A268}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -1042,7 +1045,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1057,7 +1060,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -1072,7 +1075,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1087,42 +1090,42 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -1138,48 +1141,48 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4DFFE1C-360D-4190-BB86-5F5E0C9679EC}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>10</v>
       </c>
       <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>33</v>
       </c>
-      <c r="L1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>34</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>35</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>36</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>37</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>38</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>39</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>40</v>
       </c>
-      <c r="H3" t="s">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>42</v>
       </c>
       <c r="B4" s="6">
         <v>0.85199999999999998</v>
@@ -1200,9 +1203,9 @@
         <v>0.31900000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5">
         <v>0.56299999999999994</v>
@@ -1223,9 +1226,9 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
         <v>0.23799999999999999</v>
@@ -1246,9 +1249,9 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7">
         <v>0.16900000000000001</v>
@@ -1269,9 +1272,9 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8">
         <f>SUM(B5:B7)</f>
@@ -1302,9 +1305,9 @@
         <v>2.3908</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9">
         <f>B8/H8</f>
@@ -1327,9 +1330,9 @@
         <v>0.4550777982265351</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13">
         <f xml:space="preserve"> AVERAGE(B9:F9)</f>
@@ -1344,9 +1347,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89ECBC05-C073-46C9-8518-60F9C8C529EA}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -1366,7 +1369,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1384,7 +1387,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -1399,7 +1402,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>

--- a/Data/appliance_efficiencies.xlsx
+++ b/Data/appliance_efficiencies.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud-my.sharepoint.com/personal/dominic_jones_grattaninstitute_edu_au/Documents/Energy/Analysis/analysis_cp_dj_2025/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="8_{2735264D-2E0F-4466-B96E-5FAF4E87C276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4680F1E1-2576-4C60-A557-74B529A208AB}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="8_{2735264D-2E0F-4466-B96E-5FAF4E87C276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2DDC205-09DB-494D-8B7A-AFBFE7FDE07B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5D07E076-C928-4160-91FA-0417357B04A5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{5D07E076-C928-4160-91FA-0417357B04A5}"/>
   </bookViews>
   <sheets>
     <sheet name="coefficients" sheetId="5" r:id="rId1"/>
     <sheet name="hot water" sheetId="1" r:id="rId2"/>
     <sheet name="space heating" sheetId="3" r:id="rId3"/>
-    <sheet name="cooking" sheetId="6" r:id="rId4"/>
-    <sheet name="cooking_archive" sheetId="4" r:id="rId5"/>
+    <sheet name="space_heating_2.0" sheetId="7" r:id="rId4"/>
+    <sheet name="cooking" sheetId="6" r:id="rId5"/>
+    <sheet name="cooking_archive" sheetId="4" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="1" hidden="1">'hot water'!$A$1:$C$7</definedName>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="76">
   <si>
     <t>Grid electricity
 kWh/year</t>
@@ -217,6 +218,72 @@
   </si>
   <si>
     <t>Space conditioning - heating</t>
+  </si>
+  <si>
+    <t>alternative?</t>
+  </si>
+  <si>
+    <t>https://cdn.prod.website-files.com/612b0b172765f9c62c1c20c9/67d24b1b1b250415e33183ea_2025%20Fact%20sheet%20-%20Space%20heating.pdf%20(2).pdf</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Working Family - gas - MJ</t>
+  </si>
+  <si>
+    <t>Working family - electric - kwh</t>
+  </si>
+  <si>
+    <t>ratio</t>
+  </si>
+  <si>
+    <t>Adelaide</t>
+  </si>
+  <si>
+    <t>Armidale</t>
+  </si>
+  <si>
+    <t>Bairnsdale</t>
+  </si>
+  <si>
+    <t>Bega</t>
+  </si>
+  <si>
+    <t>Bendigo</t>
+  </si>
+  <si>
+    <t>Canberra</t>
+  </si>
+  <si>
+    <t>Dubbo</t>
+  </si>
+  <si>
+    <t>Hobart</t>
+  </si>
+  <si>
+    <t>Melbourne</t>
+  </si>
+  <si>
+    <t>Mildura</t>
+  </si>
+  <si>
+    <t>Sydney</t>
+  </si>
+  <si>
+    <t>Toowoomba</t>
+  </si>
+  <si>
+    <t>Wagga Wagga</t>
+  </si>
+  <si>
+    <t>Warrnambool</t>
+  </si>
+  <si>
+    <t>Wodonga</t>
+  </si>
+  <si>
+    <t>Table 8 and 9</t>
   </si>
 </sst>
 </file>
@@ -406,10 +473,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{F348179D-7ECA-4E0E-AEA5-931FFAF660D8}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="14" unboundColumnsRight="3">
@@ -443,7 +506,7 @@
     <tableColumn id="3" xr3:uid="{2366685C-CA52-4679-A8AD-B1010B5DD6D1}" uniqueName="3" name="Gas usage_x000a_MJ/yr" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{AAFB38E1-8F68-4B98-B886-B437B61B2B9C}" uniqueName="4" name="gas usage kwh" queryTableFieldId="11" dataDxfId="2">
       <calculatedColumnFormula>Table003__Page_3[[#This Row],[Gas usage
-MJ/yr]]*0.278</calculatedColumnFormula>
+MJ/yr]]/3.6</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{F53BFD95-5465-46AA-8464-52394A4C1258}" uniqueName="5" name="total_energy_kwh" queryTableFieldId="12" dataDxfId="1">
       <calculatedColumnFormula>Table003__Page_3[[#This Row],[Grid electricity
@@ -774,14 +837,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84206C80-EF8B-460E-AD2F-5661B8B796F3}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>28</v>
       </c>
@@ -789,7 +852,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -800,26 +863,29 @@
       <c r="C2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="N2">
+        <f>0.8/0.94</f>
+        <v>0.85106382978723416</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>31</v>
       </c>
       <c r="B3">
         <f>'hot water'!F4</f>
-        <v>0.80584122538955694</v>
+        <v>0.8064753688750953</v>
       </c>
       <c r="C3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>53</v>
       </c>
       <c r="B4">
-        <f>'space heating'!C4</f>
-        <v>0.24109589041095891</v>
+        <v>0.15</v>
       </c>
       <c r="C4" t="s">
         <v>52</v>
@@ -867,7 +933,7 @@
       </c>
       <c r="D2">
         <f>Table003__Page_3[[#This Row],[Gas usage
-MJ/yr]]*0.278</f>
+MJ/yr]]/3.6</f>
         <v>0</v>
       </c>
       <c r="E2">
@@ -895,17 +961,17 @@
       </c>
       <c r="D3">
         <f>Table003__Page_3[[#This Row],[Gas usage
-MJ/yr]]*0.278</f>
-        <v>4496.6500000000005</v>
+MJ/yr]]/3.6</f>
+        <v>4493.0555555555557</v>
       </c>
       <c r="E3">
         <f>Table003__Page_3[[#This Row],[Grid electricity
 kWh/year]]+Table003__Page_3[[#This Row],[gas usage kwh]]</f>
-        <v>4496.6500000000005</v>
+        <v>4493.0555555555557</v>
       </c>
       <c r="F3">
         <f>3407/Table003__Page_3[[#This Row],[total_energy_kwh]]</f>
-        <v>0.75767515817330666</v>
+        <v>0.75828129829984547</v>
       </c>
       <c r="M3" t="s">
         <v>27</v>
@@ -923,17 +989,17 @@
       </c>
       <c r="D4">
         <f>Table003__Page_3[[#This Row],[Gas usage
-MJ/yr]]*0.278</f>
-        <v>4158.88</v>
+MJ/yr]]/3.6</f>
+        <v>4155.5555555555557</v>
       </c>
       <c r="E4">
         <f>Table003__Page_3[[#This Row],[Grid electricity
 kWh/year]]+Table003__Page_3[[#This Row],[gas usage kwh]]</f>
-        <v>4227.88</v>
+        <v>4224.5555555555557</v>
       </c>
       <c r="F4">
         <f>3407/Table003__Page_3[[#This Row],[total_energy_kwh]]</f>
-        <v>0.80584122538955694</v>
+        <v>0.8064753688750953</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -948,7 +1014,7 @@
       </c>
       <c r="D5">
         <f>Table003__Page_3[[#This Row],[Gas usage
-MJ/yr]]*0.278</f>
+MJ/yr]]/3.6</f>
         <v>0</v>
       </c>
       <c r="E5">
@@ -973,7 +1039,7 @@
       </c>
       <c r="D6">
         <f>Table003__Page_3[[#This Row],[Gas usage
-MJ/yr]]*0.278</f>
+MJ/yr]]/3.6</f>
         <v>0</v>
       </c>
       <c r="E6">
@@ -998,7 +1064,7 @@
       </c>
       <c r="D7">
         <f>Table003__Page_3[[#This Row],[Gas usage
-MJ/yr]]*0.278</f>
+MJ/yr]]/3.6</f>
         <v>0</v>
       </c>
       <c r="E7">
@@ -1074,6 +1140,12 @@
       <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="J3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -1133,12 +1205,379 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="K1" r:id="rId1" xr:uid="{E57F3D2C-EF9C-40E8-9AB6-16DF6CE7A1F9}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{E95D2ABE-D330-451A-AA38-79442D4DE8B5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC719690-207E-47A0-B2CD-6CDBAAA2EE79}">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="1">
+        <v>30196</v>
+      </c>
+      <c r="C2" s="1">
+        <f>B2*0.278</f>
+        <v>8394.4880000000012</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2">
+        <v>1295</v>
+      </c>
+      <c r="H2">
+        <f>E2/C2</f>
+        <v>0.15426789579066644</v>
+      </c>
+      <c r="K2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="1">
+        <v>59041</v>
+      </c>
+      <c r="C3" s="1">
+        <f t="shared" ref="C3:C16" si="0">B3*0.278</f>
+        <v>16413.398000000001</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3">
+        <v>2121</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H16" si="1">E3/C3</f>
+        <v>0.12922369883433033</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="1">
+        <v>60039</v>
+      </c>
+      <c r="C4" s="1">
+        <f t="shared" si="0"/>
+        <v>16690.842000000001</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4">
+        <v>2177</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="1"/>
+        <v>0.1304308075050977</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="1">
+        <v>35312</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" si="0"/>
+        <v>9816.7360000000008</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5">
+        <v>1447</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>0.14740133584115941</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="1">
+        <v>70560</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" si="0"/>
+        <v>19615.68</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6">
+        <v>2442</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>0.1244922429403416</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="1">
+        <v>55671</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" si="0"/>
+        <v>15476.538000000002</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7">
+        <v>2077</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>0.13420314026302263</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="1">
+        <v>32141</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" si="0"/>
+        <v>8935.1980000000003</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8">
+        <v>1380</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>0.15444537434984651</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="1">
+        <v>69478</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" si="0"/>
+        <v>19314.884000000002</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9">
+        <v>2379</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>0.12316926159121638</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46753</v>
+      </c>
+      <c r="C10" s="1">
+        <f t="shared" si="0"/>
+        <v>12997.334000000001</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10">
+        <v>1758</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>0.13525850762933384</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="1">
+        <v>32241</v>
+      </c>
+      <c r="C11" s="1">
+        <f t="shared" si="0"/>
+        <v>8962.9980000000014</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11">
+        <v>1404</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>0.15664401576347556</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="1">
+        <v>12221</v>
+      </c>
+      <c r="C12" s="1">
+        <f t="shared" si="0"/>
+        <v>3397.4380000000001</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12">
+        <v>824</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>0.24253569895903912</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="1">
+        <v>25120</v>
+      </c>
+      <c r="C13" s="1">
+        <f t="shared" si="0"/>
+        <v>6983.3600000000006</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13">
+        <v>1171</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>0.16768432387847682</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="1">
+        <v>45998</v>
+      </c>
+      <c r="C14" s="1">
+        <f t="shared" si="0"/>
+        <v>12787.444000000001</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14">
+        <v>1781</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>0.13927724727474855</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="1">
+        <v>69115</v>
+      </c>
+      <c r="C15" s="1">
+        <f t="shared" si="0"/>
+        <v>19213.97</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15">
+        <v>2351</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>0.12235888783005282</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="1">
+        <v>48526</v>
+      </c>
+      <c r="C16" s="1">
+        <f t="shared" si="0"/>
+        <v>13490.228000000001</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16">
+        <v>1848</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>0.13698804794107258</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K1" r:id="rId1" xr:uid="{74EB85AD-B41D-4B77-99B4-0DA6E1E03AF9}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4DFFE1C-360D-4190-BB86-5F5E0C9679EC}">
   <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1344,7 +1783,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89ECBC05-C073-46C9-8518-60F9C8C529EA}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>

--- a/Data/appliance_efficiencies.xlsx
+++ b/Data/appliance_efficiencies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud-my.sharepoint.com/personal/dominic_jones_grattaninstitute_edu_au/Documents/Energy/Analysis/analysis_cp_dj_2025/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="8_{2735264D-2E0F-4466-B96E-5FAF4E87C276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2DDC205-09DB-494D-8B7A-AFBFE7FDE07B}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="8_{2735264D-2E0F-4466-B96E-5FAF4E87C276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9F5EBA4-7CEE-4381-9777-EB0EE861225A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{5D07E076-C928-4160-91FA-0417357B04A5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{5D07E076-C928-4160-91FA-0417357B04A5}"/>
   </bookViews>
   <sheets>
     <sheet name="coefficients" sheetId="5" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="81">
   <si>
     <t>Grid electricity
 kWh/year</t>
@@ -284,6 +284,21 @@
   </si>
   <si>
     <t>Table 8 and 9</t>
+  </si>
+  <si>
+    <t>page 5</t>
+  </si>
+  <si>
+    <t>https://ieefa.org/media/5488/download</t>
+  </si>
+  <si>
+    <t>Climate Council furnace efficiency * ducted losses (20%)</t>
+  </si>
+  <si>
+    <t>https://www.climatechoices.act.gov.au/energy/energy-efficiency/heating-for-your-home</t>
+  </si>
+  <si>
+    <t>"As much as 30% of heat can be lost through ducting</t>
   </si>
 </sst>
 </file>
@@ -885,7 +900,8 @@
         <v>53</v>
       </c>
       <c r="B4">
-        <v>0.15</v>
+        <f>'space heating'!C4</f>
+        <v>0.19287671232876716</v>
       </c>
       <c r="C4" t="s">
         <v>52</v>
@@ -1088,10 +1104,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B1B825-ADD3-43AD-A4F4-B092E031A268}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -1108,10 +1124,13 @@
         <v>10</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="L1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1126,7 +1145,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -1147,65 +1166,77 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="3">
-        <v>0.88</v>
+        <f>0.88 *0.8</f>
+        <v>0.70400000000000007</v>
       </c>
       <c r="C4" s="4">
         <f t="shared" si="0"/>
-        <v>0.24109589041095891</v>
+        <v>0.19287671232876716</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J8" t="s">
+        <v>79</v>
+      </c>
+      <c r="R8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K1" r:id="rId1" xr:uid="{E57F3D2C-EF9C-40E8-9AB6-16DF6CE7A1F9}"/>
-    <hyperlink ref="K3" r:id="rId2" xr:uid="{E95D2ABE-D330-451A-AA38-79442D4DE8B5}"/>
+    <hyperlink ref="K3" r:id="rId1" xr:uid="{E95D2ABE-D330-451A-AA38-79442D4DE8B5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/appliance_efficiencies.xlsx
+++ b/Data/appliance_efficiencies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud-my.sharepoint.com/personal/dominic_jones_grattaninstitute_edu_au/Documents/Energy/Analysis/analysis_cp_dj_2025/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="8_{2735264D-2E0F-4466-B96E-5FAF4E87C276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9F5EBA4-7CEE-4381-9777-EB0EE861225A}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="8_{2735264D-2E0F-4466-B96E-5FAF4E87C276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03B5B2D6-1F63-41AC-BFA1-6F968826316B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{5D07E076-C928-4160-91FA-0417357B04A5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5D07E076-C928-4160-91FA-0417357B04A5}"/>
   </bookViews>
   <sheets>
     <sheet name="coefficients" sheetId="5" r:id="rId1"/>
@@ -1126,7 +1126,7 @@
       <c r="K1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="K5" t="s">
+      <c r="K5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="J8" t="s">
+      <c r="J8" s="2" t="s">
         <v>79</v>
       </c>
       <c r="R8" t="s">
@@ -1237,6 +1237,9 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="K3" r:id="rId1" xr:uid="{E95D2ABE-D330-451A-AA38-79442D4DE8B5}"/>
+    <hyperlink ref="L1" r:id="rId2" xr:uid="{D3F73B48-5DAA-4B92-885B-63CB6D84832F}"/>
+    <hyperlink ref="K5" r:id="rId3" xr:uid="{97312A5F-30C3-4B40-969D-4279F82A25DE}"/>
+    <hyperlink ref="J8" r:id="rId4" xr:uid="{F121F97B-4DE2-4BFD-A8E8-E23B18989C69}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1617,7 +1620,7 @@
       <c r="A1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>32</v>
       </c>
       <c r="L1" t="s">
@@ -1810,6 +1813,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B1" r:id="rId1" xr:uid="{0B458818-0376-40B8-83F1-6D68F62C81A8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Data/appliance_efficiencies.xlsx
+++ b/Data/appliance_efficiencies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud-my.sharepoint.com/personal/dominic_jones_grattaninstitute_edu_au/Documents/Energy/Analysis/analysis_cp_dj_2025/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="8_{2735264D-2E0F-4466-B96E-5FAF4E87C276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03B5B2D6-1F63-41AC-BFA1-6F968826316B}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="8_{2735264D-2E0F-4466-B96E-5FAF4E87C276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A78FC6F7-03F5-42F0-9EB7-4EC80FA9FC05}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5D07E076-C928-4160-91FA-0417357B04A5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{5D07E076-C928-4160-91FA-0417357B04A5}"/>
   </bookViews>
   <sheets>
     <sheet name="coefficients" sheetId="5" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="82">
   <si>
     <t>Grid electricity
 kWh/year</t>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>"As much as 30% of heat can be lost through ducting</t>
+  </si>
+  <si>
+    <t>inverse</t>
   </si>
 </sst>
 </file>
@@ -351,7 +354,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -359,12 +362,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -488,16 +495,21 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{F348179D-7ECA-4E0E-AEA5-931FFAF660D8}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="14" unboundColumnsRight="3">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="15" unboundColumnsRight="4">
+    <queryTableFields count="7">
       <queryTableField id="1" name="Hot water system type" tableColumnId="1"/>
       <queryTableField id="2" name="Grid electricity_x000a_kWh/year" tableColumnId="2"/>
       <queryTableField id="3" name="Gas usage_x000a_MJ/yr" tableColumnId="3"/>
       <queryTableField id="11" dataBound="0" tableColumnId="4"/>
       <queryTableField id="12" dataBound="0" tableColumnId="5"/>
       <queryTableField id="13" dataBound="0" tableColumnId="6"/>
+      <queryTableField id="14" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
     <queryTableDeletedFields count="7">
       <deletedField name="SYD"/>
@@ -513,22 +525,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A910C31-2886-4BA8-A03F-6F231AD33192}" name="Table003__Page_3" displayName="Table003__Page_3" ref="A1:F7" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F7" xr:uid="{1A910C31-2886-4BA8-A03F-6F231AD33192}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{0DF37097-27F2-4928-B532-D34BA572AB21}" uniqueName="1" name="appliance" queryTableFieldId="1" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A910C31-2886-4BA8-A03F-6F231AD33192}" name="Table003__Page_3" displayName="Table003__Page_3" ref="A1:G7" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G7" xr:uid="{1A910C31-2886-4BA8-A03F-6F231AD33192}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{0DF37097-27F2-4928-B532-D34BA572AB21}" uniqueName="1" name="appliance" queryTableFieldId="1" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{4C3DAD1E-D93E-4AEC-B0F9-C070A9898F00}" uniqueName="2" name="Grid electricity_x000a_kWh/year" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{2366685C-CA52-4679-A8AD-B1010B5DD6D1}" uniqueName="3" name="Gas usage_x000a_MJ/yr" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{AAFB38E1-8F68-4B98-B886-B437B61B2B9C}" uniqueName="4" name="gas usage kwh" queryTableFieldId="11" dataDxfId="2">
+    <tableColumn id="4" xr3:uid="{AAFB38E1-8F68-4B98-B886-B437B61B2B9C}" uniqueName="4" name="gas usage kwh" queryTableFieldId="11" dataDxfId="3">
       <calculatedColumnFormula>Table003__Page_3[[#This Row],[Gas usage
 MJ/yr]]/3.6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F53BFD95-5465-46AA-8464-52394A4C1258}" uniqueName="5" name="total_energy_kwh" queryTableFieldId="12" dataDxfId="1">
+    <tableColumn id="5" xr3:uid="{F53BFD95-5465-46AA-8464-52394A4C1258}" uniqueName="5" name="total_energy_kwh" queryTableFieldId="12" dataDxfId="2">
       <calculatedColumnFormula>Table003__Page_3[[#This Row],[Grid electricity
 kWh/year]]+Table003__Page_3[[#This Row],[gas usage kwh]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{80355AFB-10B3-4D58-A29E-41B38455A143}" uniqueName="6" name="coeff" queryTableFieldId="13" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{80355AFB-10B3-4D58-A29E-41B38455A143}" uniqueName="6" name="coeff" queryTableFieldId="13" dataDxfId="1">
       <calculatedColumnFormula>3407/Table003__Page_3[[#This Row],[total_energy_kwh]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{00D13A91-DA7D-4D26-A57E-4A07D9852FE7}" uniqueName="7" name="inverse" queryTableFieldId="14" dataDxfId="0">
+      <calculatedColumnFormula xml:space="preserve"> 1/ Table003__Page_3[[#This Row],[coeff]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -936,6 +951,12 @@
       <c r="F1" t="s">
         <v>21</v>
       </c>
+      <c r="G1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -961,6 +982,14 @@
         <f>3407/Table003__Page_3[[#This Row],[total_energy_kwh]]</f>
         <v>1</v>
       </c>
+      <c r="G2" s="7">
+        <f xml:space="preserve"> 1/ Table003__Page_3[[#This Row],[coeff]]</f>
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <f>1 /G4</f>
+        <v>0.8064753688750953</v>
+      </c>
       <c r="M2" t="s">
         <v>8</v>
       </c>
@@ -989,6 +1018,10 @@
         <f>3407/Table003__Page_3[[#This Row],[total_energy_kwh]]</f>
         <v>0.75828129829984547</v>
       </c>
+      <c r="G3" s="7">
+        <f xml:space="preserve"> 1/ Table003__Page_3[[#This Row],[coeff]]</f>
+        <v>1.3187718096728955</v>
+      </c>
       <c r="M3" t="s">
         <v>27</v>
       </c>
@@ -1017,6 +1050,10 @@
         <f>3407/Table003__Page_3[[#This Row],[total_energy_kwh]]</f>
         <v>0.8064753688750953</v>
       </c>
+      <c r="G4" s="7">
+        <f xml:space="preserve"> 1/ Table003__Page_3[[#This Row],[coeff]]</f>
+        <v>1.2399634738936178</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1042,6 +1079,10 @@
         <f>3407/Table003__Page_3[[#This Row],[total_energy_kwh]]</f>
         <v>6.6803921568627453</v>
       </c>
+      <c r="G5" s="7">
+        <f xml:space="preserve"> 1/ Table003__Page_3[[#This Row],[coeff]]</f>
+        <v>0.14969181097739948</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -1067,6 +1108,10 @@
         <f>3407/Table003__Page_3[[#This Row],[total_energy_kwh]]</f>
         <v>4.500660501981506</v>
       </c>
+      <c r="G6" s="7">
+        <f xml:space="preserve"> 1/ Table003__Page_3[[#This Row],[coeff]]</f>
+        <v>0.22218960962723802</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -1091,6 +1136,10 @@
       <c r="F7">
         <f>3407/Table003__Page_3[[#This Row],[total_energy_kwh]]</f>
         <v>1.9237718802936195</v>
+      </c>
+      <c r="G7" s="7">
+        <f xml:space="preserve"> 1/ Table003__Page_3[[#This Row],[coeff]]</f>
+        <v>0.51981215145289106</v>
       </c>
     </row>
   </sheetData>
@@ -1106,6 +1155,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B1B825-ADD3-43AD-A4F4-B092E031A268}">
   <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.75" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
